--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45761</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45359</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45288</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>44645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45338</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45149</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46125</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45581</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45359</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45359</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45065</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44629</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45706</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45723</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44936</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44840</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>46125</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>46260</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45706</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44462</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44539</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44482</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44767</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44819</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44538</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45632</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45632</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44543</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45596</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45280</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44967</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>44992</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44600</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45035</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45359</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44925</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45653</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>45659</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45749</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45371</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>45400</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44613</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45461</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45721</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45532</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45242</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45242</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45726</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45014</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45743</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45071</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45370</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45099</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45656</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45071</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45729</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45867</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44895</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44767</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45888</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45699</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45726</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45888</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45889</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44789</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44851</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45359</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45359</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45691</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45532</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>45532</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45205</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45820</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>45323</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45728</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45912</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45726</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>46001</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45922</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44748</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45922</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45253</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45744</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45930</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45371</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45371</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45749</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>44775</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45701</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45940</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45356</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>46149</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45950</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45329</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45952</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>44539</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45960</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45656</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45656</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45742</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44869</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45103</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>45968</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45756</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>45607</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>44897</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44994</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45096</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45160</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45398</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45993</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45617</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45741</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>44971</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>44726</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45219</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45366</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>46002</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>44593</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44942</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45204</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45755</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45706</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45881</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45700</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>46150</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>46027</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45113</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>46031</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>46031</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45656</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46031</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45638</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>45078</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44873</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45436</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>46176</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>46176</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>46176</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>46176</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>46176</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45728</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45719</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45719</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46052</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>46054</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>46054</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46054</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45525</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45922</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>45335</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>46066</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45729</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45504</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44601</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46077</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45560</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>46078</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>46078</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>46078</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45639</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>46184</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>46184</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>46184</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>46184</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>46184</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>46184</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>46184</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45131</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45131</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>46086</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45719</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44773</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>46197</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>44467</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>46197</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45756</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45461</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>46125</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>44684</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45743</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45653</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45653</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45008</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45246</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45801</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45936</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45504</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45922</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45587</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>44467</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45706</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45371</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>44997</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>45275</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45510</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45323</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45208</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>44468</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45398</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45096</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>44869</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>46258</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>46258</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>46260</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44777</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>46260</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>46260</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>46260</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>46260</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45596</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44831</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45749</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45646</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45288</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44992</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44693</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44925</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45698</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>44999</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45777</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>46269</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45777</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45776</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>46232</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45610</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45792</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45679</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45800</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45265</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45776</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45817</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45103</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45819</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45820</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45839</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45845</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>45846</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45846</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45848</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45849</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45855</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45861</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45761</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>45862</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45134</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45537</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45700</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45524</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45524</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45576</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>44925</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22910,7 +22910,7 @@
         <v>45561</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45639</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45478</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45365</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45847</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45091</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45440</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45337</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45337</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>45635</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45706</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45443</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45062</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45062</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45062</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45028</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45091</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45273</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45118</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45478</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45686</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45631</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45875</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45873</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45667</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45359</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45761</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45338</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45288</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>44645</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>46125</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45581</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45744</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45149</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45737</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45749</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>46125</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45723</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45706</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45706</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>46260</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45065</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44936</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45359</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44482</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44767</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44819</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44538</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45719</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44869</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45330</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45756</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45370</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>44767</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45436</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44925</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44467</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45504</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>46027</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45679</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44467</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44942</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45532</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>46031</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>46031</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45888</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>46031</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45638</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>45889</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45889</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45800</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>46052</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45280</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46054</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>46054</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44897</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45726</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44925</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45510</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>46066</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45922</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46077</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44873</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>46078</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>46078</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>46078</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45560</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44600</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45246</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45265</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>46086</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45940</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45950</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45923</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45113</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45952</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44967</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>45008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45960</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>46125</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44684</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45968</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>45706</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>45596</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45096</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45359</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45359</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45103</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45607</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>45204</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>45817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>45698</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>45726</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45699</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45743</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>45801</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45729</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>46002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45744</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45810</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45078</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45936</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>46001</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45819</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>45728</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45820</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45719</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45719</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45728</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45205</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45922</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>46000</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45726</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45691</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45071</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45461</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>46149</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44468</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44851</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45917</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45839</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44981</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45656</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45656</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45845</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45846</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45846</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45329</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45848</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45756</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>45755</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45653</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45881</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45849</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45855</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44831</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45861</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44997</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44539</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45761</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45014</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45596</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>46176</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>46176</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>46176</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>46176</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>46176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45922</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45478</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45706</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>45847</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45873</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45478</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45337</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45337</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45028</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45524</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>45524</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45400</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45631</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45686</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45440</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>46184</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>45153</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45365</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>46184</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>46184</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>46184</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>45118</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45062</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>46184</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45275</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>46184</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>46184</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45091</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45134</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45537</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45639</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45700</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45062</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45062</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45635</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45561</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45576</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44925</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45443</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45875</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>46197</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>46197</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45587</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45639</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45742</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45071</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45659</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45656</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45366</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45371</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>44601</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>44789</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>46258</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>46258</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>46260</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>46260</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>46260</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>46260</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>46260</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44613</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44773</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45096</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45632</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45632</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44726</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45719</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45719</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45749</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45743</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45288</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>46269</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44925</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45743</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45160</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>46232</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45701</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45729</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45525</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45525</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44992</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>44593</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45335</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44775</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44895</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>46150</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45371</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45359</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45323</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45356</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>44748</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>44869</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45131</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45131</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45219</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>44543</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45371</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>45371</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45743</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45398</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45398</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45099</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45242</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45242</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45656</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22910,7 +22910,7 @@
         <v>45743</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45596</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45208</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44777</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45749</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45653</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45653</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>45733</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45103</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45617</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45253</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45646</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45323</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45776</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45777</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45777</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45792</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45610</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45667</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45359</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45761</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45338</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45288</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>44645</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>46125</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45581</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45744</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45149</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45737</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45749</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>46125</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45723</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45706</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45706</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>46260</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45065</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44936</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45359</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>44629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44482</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44767</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44819</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44538</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45719</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44869</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45330</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45756</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45370</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>44767</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45436</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44925</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44467</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45504</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>46027</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45679</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44467</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44942</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45532</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>46031</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>46031</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45888</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>46031</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45638</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>45889</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45889</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45800</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>46052</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45280</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>46054</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>46054</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44897</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45726</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44925</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45510</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>46066</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45922</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46077</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44873</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>46078</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>46078</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>46078</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45560</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44600</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45246</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45265</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>46086</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45940</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45950</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45923</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45113</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45952</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44967</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>45008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45960</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>46125</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44684</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45968</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>45706</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>45596</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45096</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45359</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45359</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45103</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45607</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>45204</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>45817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>45698</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>45726</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45699</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45743</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>45801</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45729</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>46002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45744</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45810</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45078</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45936</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>46001</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45819</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>45728</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45820</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45719</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45719</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45728</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45205</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45922</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>46000</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45726</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45691</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45071</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45461</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>46149</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44468</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44851</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45917</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45839</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44981</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45656</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45656</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45845</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45846</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45846</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45329</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45848</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45756</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>45755</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45653</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45881</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45849</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45855</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44831</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45861</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44997</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44539</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45761</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45014</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45596</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>46176</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>46176</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>46176</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>46176</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>46176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45922</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45478</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45706</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>45847</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45873</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45478</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45337</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45337</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45028</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45524</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>45524</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45400</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45631</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45686</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45440</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>46184</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>45153</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45365</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>46184</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>46184</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>46184</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>45118</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45062</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>46184</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45275</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>46184</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>46184</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45091</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45134</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45537</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45639</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45700</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45062</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45062</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45635</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45561</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45576</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44925</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45443</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45875</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>46197</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>46197</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45587</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45639</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45742</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45071</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45659</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45656</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45366</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45371</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>44601</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>44789</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>46258</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>46258</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>46260</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>46260</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>46260</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>46260</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>46260</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44613</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44773</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45096</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45632</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45632</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44726</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45719</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45719</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45749</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45743</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45288</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>46269</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44925</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45743</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45160</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>46232</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45701</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45729</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45525</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45525</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44992</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>44593</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45335</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44775</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44895</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>46150</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45371</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45359</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45323</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45356</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>44748</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>44869</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45131</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45131</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45219</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>44543</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45371</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>45371</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45743</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45398</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45398</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45099</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45242</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45242</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45656</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22910,7 +22910,7 @@
         <v>45743</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45596</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45208</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44777</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45749</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45653</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45653</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>45733</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45103</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45617</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45253</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45646</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45323</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45776</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45777</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45777</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45792</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45610</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45667</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45761</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45359</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45338</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45288</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45149</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46125</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45581</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45359</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45359</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45749</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45737</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45065</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>46125</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44629</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45706</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44936</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>46260</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44482</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44767</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44819</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44538</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45632</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45632</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44543</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45280</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45596</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45330</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>44967</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45719</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44992</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44600</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>46002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45359</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45035</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45888</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45889</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45889</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44925</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44925</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>46027</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>46031</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>46031</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45653</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>46031</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45188</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44981</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>45638</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45371</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>45659</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45749</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44986</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>45912</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>45400</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45800</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>46052</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>46054</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45922</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>46054</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>46054</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44613</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45461</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45242</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45242</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>46066</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>45726</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>45014</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>45940</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>45743</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45265</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>46077</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45370</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46078</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>46078</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>46078</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45923</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45099</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45950</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45952</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45656</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>46086</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45776</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45960</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45968</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45103</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45819</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45729</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>46125</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>44895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44767</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>44684</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44789</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44851</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45359</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45359</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45801</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45936</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>45839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45504</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45532</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45532</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45922</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>45867</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>45845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>45810</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45846</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45846</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>45848</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45888</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45849</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>45323</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45699</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45726</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45855</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46000</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44748</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45253</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45691</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45205</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45861</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45820</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45371</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45371</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45749</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45761</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44775</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45701</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45728</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45356</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45134</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>45726</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45537</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45700</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>45744</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45524</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45524</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45576</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44925</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>45561</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>45639</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45365</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>45847</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>45091</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>45440</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45337</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45337</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45635</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45706</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45443</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45329</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45062</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45062</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45062</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45028</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>46149</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45743</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>44539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45273</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45118</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45686</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45631</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45656</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45656</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45875</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45742</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44869</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>45103</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>45756</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45741</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45917</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>45873</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45607</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45096</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45881</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>45700</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>44994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45160</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45398</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45617</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>46176</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>46176</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>46176</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>46176</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>46176</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>45922</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44971</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44726</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45219</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>46184</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>46184</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>46184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>46184</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>46184</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>46184</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>46184</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>46184</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45366</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44593</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44942</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45755</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>46197</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>46197</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45656</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45078</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44873</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45436</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>46258</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>46258</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>46260</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45728</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45719</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45719</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>46260</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>46260</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>46260</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>46260</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45525</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45525</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45288</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45335</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45729</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45504</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44601</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>46269</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45560</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45639</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45131</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45131</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>46232</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45719</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>44773</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>46150</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45756</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45461</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45743</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45653</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45653</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45008</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45743</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45743</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45743</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45246</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>46295</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>46295</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>46295</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>46295</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>46295</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45587</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>46297</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45706</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45371</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44997</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45275</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45510</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45323</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45208</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45398</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45096</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44869</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>44777</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45596</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44831</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45749</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45646</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44693</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44925</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45698</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45777</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45777</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45776</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45667</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45761</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45359</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45338</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45288</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45149</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46125</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45581</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45359</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45359</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45749</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45737</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45065</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>46125</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44629</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45706</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44936</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>46260</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44482</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44767</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44819</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44538</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45632</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45632</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44543</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45280</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45596</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45330</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>44967</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45719</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44992</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44600</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>46002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45359</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45035</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45888</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45889</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45889</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44925</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44925</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>46027</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>46031</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>46031</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45653</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>46031</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45188</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44981</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>45638</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45371</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>45659</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45749</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44986</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>45792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>45912</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>45400</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45800</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>46052</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>46054</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45922</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>46054</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>46054</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44613</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45461</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45242</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45242</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>46066</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>45726</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>45014</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>45940</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>45743</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45265</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>46077</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45370</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46078</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>46078</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>46078</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45923</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45099</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45950</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45952</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45656</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>46086</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45776</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45960</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45968</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45103</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45819</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45729</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>46125</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>44895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44767</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>44684</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44789</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44851</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45359</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45359</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45801</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45936</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>45839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45504</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45532</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45532</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45922</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>45867</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>45845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>45810</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45846</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45846</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>45848</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45888</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45849</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>45323</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45699</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45726</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45855</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46000</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44748</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45253</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45691</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45205</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45861</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45820</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45371</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45371</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45749</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45761</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44775</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45701</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45728</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45356</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45134</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>45726</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45537</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45700</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>45744</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45524</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45524</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45576</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44925</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>45561</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>45639</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45365</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>45847</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>45091</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>45440</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45337</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45337</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45635</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45706</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45443</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45329</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45062</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45062</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45062</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45028</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>46149</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45743</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>44539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45273</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45118</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45686</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45631</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45656</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45656</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45875</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45742</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44869</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>45103</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>45756</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45741</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45917</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>45873</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45607</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45096</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45881</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>45700</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>44994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45160</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45398</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45617</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>46176</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>46176</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>46176</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>46176</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>46176</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>45922</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44971</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44726</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45219</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>46184</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>46184</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>46184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>46184</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>46184</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>46184</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>46184</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>46184</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45366</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44593</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>44942</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45755</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>46197</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>46197</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45656</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45078</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44873</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45436</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>46258</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>46258</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>46260</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45728</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45719</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45719</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>46260</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>46260</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>46260</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>46260</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45525</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45525</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45288</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45335</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45729</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45504</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44601</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>46269</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45560</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45639</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45131</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45131</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>46232</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45719</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>44773</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>46150</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45756</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45461</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45743</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45653</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45653</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45008</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45743</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45743</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45743</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45246</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>46295</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>46295</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>46295</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>46295</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>46295</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45587</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>46297</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45706</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45371</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44997</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45275</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45510</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45323</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45208</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45398</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45096</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44869</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>44777</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45596</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44831</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45749</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45646</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44693</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44925</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45698</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45777</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45777</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45776</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45667</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45359</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45761</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45338</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45288</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45149</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45744</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45581</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>46125</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44510</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45706</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45737</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45749</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45723</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45706</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45679</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45359</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>46125</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45065</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>44936</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45359</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44482</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44819</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44767</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45719</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44543</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45330</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44869</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45371</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45371</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45743</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45398</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45398</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45099</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45242</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45242</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>44994</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45656</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45743</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45370</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45721</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44767</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45656</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45656</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45436</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>45329</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45756</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45755</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45653</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45188</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45208</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44925</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45504</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44777</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44831</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45888</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44997</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44539</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45014</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44942</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45889</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45889</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45532</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44992</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44971</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45653</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45653</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45733</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45103</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45617</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45253</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45646</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45323</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44487</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45776</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45777</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45777</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>45912</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>45400</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45280</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44994</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45275</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45726</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45510</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45922</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45922</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44999</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45792</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44873</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45560</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>44600</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45587</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45639</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45679</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44693</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45246</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45071</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45659</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45800</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45656</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>44986</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45366</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45371</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44601</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>45113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44789</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45103</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45776</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45008</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45819</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45950</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45923</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45706</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45461</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45960</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44613</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44773</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45596</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45096</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45359</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45359</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>45096</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45632</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45632</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45839</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45968</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>44726</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45846</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>45719</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>45719</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>45607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>45846</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>45204</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45848</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45698</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45749</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45743</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45849</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45855</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45743</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45743</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45861</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45761</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45729</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45078</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45478</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45706</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45847</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45873</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45478</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45337</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45337</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45028</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45524</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45524</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45631</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45686</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45440</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45365</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45118</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45062</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>45273</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45537</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45639</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45700</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45062</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45062</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45635</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44925</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45561</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45576</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45719</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45719</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>44925</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45443</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45875</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45728</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45160</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45071</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45701</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45749</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45461</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>45729</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45525</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45525</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44992</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45993</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>46125</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44684</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>44593</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45335</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>46002</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>44775</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44895</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>45371</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45888</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45359</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45323</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45356</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45699</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>44748</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>44869</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45801</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>46027</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45744</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45810</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46031</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>46031</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45936</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45131</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45131</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>46001</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>46031</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45728</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45504</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45867</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45820</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45638</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45205</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45922</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45219</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46000</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45726</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45691</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>46052</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>46054</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>46054</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>46054</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>46066</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>46149</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>46077</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>46078</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>46078</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>46078</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>46086</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45917</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45741</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45881</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45700</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>46176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>46176</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>46176</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>46176</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>46176</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45922</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>46184</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>46184</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>46184</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>46184</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>46184</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>46184</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>46184</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46184</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>46197</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45288</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46269</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46232</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>46150</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>46295</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>46295</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>46295</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46295</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46295</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>46300</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>46297</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>46258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>46258</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46260</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>46260</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>46260</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>46260</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>46260</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45667</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45359</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45761</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44645</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45338</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45288</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45149</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45744</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45581</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>46125</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44510</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44645</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45706</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45737</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45749</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45723</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>44840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45706</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45679</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45359</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>46125</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45065</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>44936</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45359</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44538</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44482</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44819</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44767</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45719</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44543</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45330</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44869</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45371</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45371</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45743</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45398</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45398</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45099</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45242</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45242</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>44994</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45656</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45743</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44981</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45370</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45721</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44767</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45656</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45656</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45436</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>45329</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45756</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45755</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45653</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45188</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45208</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44925</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45504</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44777</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44831</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45888</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44997</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44539</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45014</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44942</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45889</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45889</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45532</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44992</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44971</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45653</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45653</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45733</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45103</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45617</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45253</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45646</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45323</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44487</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45776</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45777</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45777</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>45912</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>45400</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45280</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44994</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45275</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45726</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45510</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45922</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45922</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44999</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45792</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44873</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45560</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>44600</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45587</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45639</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45679</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44693</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45246</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45071</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45659</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45800</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45656</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>44986</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45366</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45371</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44601</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>45113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44789</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45103</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45776</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45008</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45817</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45819</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45950</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45923</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45706</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45461</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45960</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44613</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44773</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45596</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45096</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45359</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45359</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>45096</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45632</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45632</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45839</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45968</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>44726</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45846</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>45719</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>45719</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>45607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>45846</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>45204</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45848</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45698</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45749</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45743</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45849</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45855</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45743</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45743</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45861</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45761</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45729</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45078</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45478</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45706</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45847</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45873</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45478</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45337</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45337</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45028</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45524</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45524</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45631</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45686</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45440</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45365</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45118</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45062</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>45273</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45537</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45639</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45700</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45062</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45062</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45635</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44925</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45561</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45576</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45719</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45719</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>44925</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45443</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45875</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45728</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45160</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45071</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45701</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45749</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45461</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>45729</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45525</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45525</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44992</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45993</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>46125</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44684</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>44593</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45335</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>46002</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>44775</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44895</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>45371</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45888</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45359</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45323</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45356</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45699</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>44748</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>44869</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45801</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>46027</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45744</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45810</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46031</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>46031</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45936</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45131</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45131</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>46001</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>46031</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45728</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45504</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45867</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45820</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45638</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45205</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45922</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45219</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46000</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45726</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45691</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>46052</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>46054</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>46054</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>46054</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>46066</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>46149</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>46077</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>46078</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>46078</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>46078</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>46086</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45917</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45741</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45881</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45700</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>46176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>46176</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>46176</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>46176</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>46176</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45922</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>46184</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>46184</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>46184</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>46184</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>46184</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>46184</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>46184</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46184</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>46197</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45288</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46269</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46232</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>46150</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>46295</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>46295</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>46295</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46295</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46295</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>46300</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>46297</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>46258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>46258</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46260</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>46260</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>46260</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>46260</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>46260</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45667</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45761</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45359</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45288</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>44645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45338</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45149</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46125</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45581</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45359</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45359</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45065</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44629</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45706</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45723</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44936</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>46125</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>44840</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>46260</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45706</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44767</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44819</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45632</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45632</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44543</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45330</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>44967</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45719</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44992</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44600</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45359</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45035</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45733</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45653</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44925</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44925</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45659</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45749</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44986</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>45371</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45400</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44613</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45461</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45721</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45532</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45242</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45242</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45726</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45014</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45743</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45071</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45370</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44487</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45099</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45656</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45071</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45596</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45729</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45867</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45888</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45726</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44895</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44767</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>46000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45888</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45889</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45691</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45205</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45728</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44789</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45359</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45359</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46001</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45744</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45532</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>45532</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45912</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45922</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45323</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>46149</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44748</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45253</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45371</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45371</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45749</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45923</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44775</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45952</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45701</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45960</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45356</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45741</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45917</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45968</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45329</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45743</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44539</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45656</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45656</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45742</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44869</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45103</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45756</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45607</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44897</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44994</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>45881</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45700</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45096</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>46002</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45160</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45398</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45617</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44971</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>46027</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44726</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>46031</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>46031</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>46031</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45219</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>46176</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>46176</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>46176</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>46176</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>46176</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45638</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45366</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45922</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>44593</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44942</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46052</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45204</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>46054</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>46054</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46054</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45755</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>46184</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>46184</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>46184</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>46184</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>46184</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46184</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>46184</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>46184</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>46066</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45113</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>46077</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46078</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45656</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>46078</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46078</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45078</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>46086</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44873</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45436</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45719</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>46197</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45525</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45525</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>46197</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45335</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45729</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>46125</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44684</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45504</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44601</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45560</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45639</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45131</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45131</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45801</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45719</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45504</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45922</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44773</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45756</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45288</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45461</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45743</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45653</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45653</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45008</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>46232</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45743</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45743</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45743</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>45246</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45587</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45706</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>46150</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45371</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44997</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>45275</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45510</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45323</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45208</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45398</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45096</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>44869</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44777</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>46295</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>46295</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45596</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45749</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>46295</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>46295</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>46295</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45646</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44992</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44693</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>44925</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46297</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45698</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44999</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45777</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45777</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45776</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46258</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>46300</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46260</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46260</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>46258</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45610</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46260</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46260</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>46260</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45792</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>46307</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45679</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45993</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45800</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45265</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>46309</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45776</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>46269</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45817</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45103</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45819</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45839</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45846</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45846</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45848</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45849</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45855</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45861</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45761</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45537</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45700</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45524</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45524</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45576</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44925</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45561</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45639</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45478</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45365</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45847</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45440</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45337</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45337</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45635</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45706</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45443</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45062</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45062</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45062</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45028</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45153</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45091</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45273</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45118</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45478</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45686</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45631</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45875</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45873</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45667</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45761</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45359</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45288</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>44645</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45338</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45744</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45149</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46125</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45581</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45359</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45359</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45065</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44629</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45706</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45723</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44936</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>46125</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>44840</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>46260</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45706</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44767</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44819</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45632</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45632</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44543</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45330</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>44967</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45719</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44992</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44600</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45359</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45035</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45733</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45653</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44925</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44925</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45659</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45749</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44986</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>45371</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45400</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44613</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45461</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45721</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45532</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45242</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45242</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45726</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45014</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45743</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45071</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45370</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44487</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45099</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45656</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45071</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45596</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45729</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45867</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45888</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45726</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44895</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44767</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>46000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45888</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45889</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45691</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45205</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45728</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44789</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45359</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45359</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46001</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45744</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45532</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>45532</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45912</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45922</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45323</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>46149</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44748</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45253</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45371</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45371</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45749</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45923</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44775</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45952</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45701</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45960</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45356</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45741</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45917</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45968</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45329</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45743</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44539</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45656</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45656</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45742</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44869</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45103</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45756</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45607</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44897</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44994</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>45881</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45700</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45096</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>46002</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45160</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45398</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45617</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44971</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>46027</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44726</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>46031</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>46031</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>46031</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45219</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>46176</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>46176</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>46176</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>46176</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>46176</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45638</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45366</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45922</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>44593</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44942</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46052</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45204</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>46054</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>46054</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46054</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45755</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>46184</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>46184</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>46184</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>46184</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>46184</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46184</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>46184</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>46184</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>46066</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45113</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>46077</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46078</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45656</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>46078</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46078</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45078</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>46086</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44873</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45436</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45719</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>46197</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45525</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45525</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>46197</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45335</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45729</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>46125</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44684</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45504</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44601</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45560</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45639</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45131</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45131</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45801</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45719</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45504</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45922</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44773</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45756</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45288</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45461</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45743</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45653</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45653</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45008</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>46232</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45743</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45743</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45743</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>45246</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45587</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45706</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>46150</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45371</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44997</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>45275</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45510</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45323</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45208</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45398</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45096</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>44869</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44777</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>46295</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>46295</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45596</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45749</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>46295</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>46295</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>46295</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45646</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44992</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44693</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>44925</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46297</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45698</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44999</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45777</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45777</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45776</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46258</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>46300</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46260</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46260</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>46258</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45610</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46260</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46260</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>46260</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45792</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>46307</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45679</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45993</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45800</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45265</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>46309</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45776</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>46269</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45817</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45103</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45819</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45839</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45846</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45846</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45848</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45849</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45855</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45861</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45761</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45537</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45700</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45524</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45524</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45576</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44925</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45561</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45639</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45478</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45365</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45847</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45440</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45337</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45337</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45635</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45706</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45443</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45062</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45062</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45062</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45028</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45153</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45091</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45273</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45118</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45478</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45686</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45631</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45875</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45873</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45667</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45359</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45761</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45288</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>44645</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45338</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>45659</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45149</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45581</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46125</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45744</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45065</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>44936</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45359</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>44629</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45737</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45749</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>45706</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46125</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46260</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45706</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45679</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44767</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44819</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45889</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45889</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45323</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45356</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44748</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44869</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45912</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45131</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45131</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45035</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45330</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44543</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>46176</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>46176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>46176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45756</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>46176</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>45370</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45371</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>45371</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45743</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44767</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>45922</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45950</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>45923</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>45398</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45398</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>45952</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45099</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>46184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>45242</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>45242</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>46184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>46184</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>46184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45656</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>45743</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45596</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46184</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>46184</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45960</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>45968</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45188</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45208</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>46197</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>46197</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44777</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44925</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45749</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45653</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45653</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45733</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45103</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45617</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45253</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45646</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45323</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>46002</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>45777</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>45777</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45288</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>46232</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45504</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>46027</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>46031</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46031</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45792</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>46031</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>45610</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45638</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>45679</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>46150</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45800</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>46052</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>46054</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>46054</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>46054</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>46066</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45103</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>45776</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45817</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45819</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>46295</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>46077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>46295</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>46078</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>46078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>46078</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>46295</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>46295</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46295</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46300</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46086</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45839</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44942</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45532</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45532</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45532</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45846</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46297</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45846</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45848</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46258</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45849</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44971</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>46258</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45855</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45861</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45761</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>46260</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>46260</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>46260</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45478</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45706</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45847</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45873</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>45478</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45337</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45337</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>46260</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45028</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45524</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45631</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46125</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45686</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45440</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45153</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45365</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45091</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45118</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45062</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45091</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45134</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45537</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45639</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45700</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45062</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45062</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45635</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45561</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>44684</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45576</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44925</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45443</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>46260</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45875</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>46307</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45888</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>44994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45726</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45726</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>46309</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44925</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45699</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45510</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45801</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45744</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45810</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>46269</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>46001</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45728</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45504</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45820</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44873</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45205</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45922</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45560</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>44600</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>46000</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44693</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45691</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45246</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>44986</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46149</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44967</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45008</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45706</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45461</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45596</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45096</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45359</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45359</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45204</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45698</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45743</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45743</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45729</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45078</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45719</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45719</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45728</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45071</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45749</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45461</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44851</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44994</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45656</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>45656</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45329</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45756</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45755</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45653</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>44831</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>44997</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>44539</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45014</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45596</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45400</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45275</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>44999</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45587</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45639</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45742</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45659</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45656</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45366</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>45371</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44601</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>44789</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44613</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>44773</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45096</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45632</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45632</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>44726</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45719</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45719</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45749</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45743</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44925</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45743</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45160</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45701</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45729</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45525</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45525</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44593</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45335</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44775</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44895</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45667</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>

--- a/Översikt KUNGSBACKA.xlsx
+++ b/Översikt KUNGSBACKA.xlsx
@@ -601,7 +601,7 @@
         <v>44509</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45359</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45761</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45197</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45288</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>44645</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45338</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>45659</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45149</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45581</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46125</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45744</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>44510</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45065</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>44936</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45359</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>44629</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45737</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45749</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>45706</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46125</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46260</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45706</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45679</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44804</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44613</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44767</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44819</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44538</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45889</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45889</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45323</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45356</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44748</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44869</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45912</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45131</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45131</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45035</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45700</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45330</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44543</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>46176</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>46176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>46176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>46176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45756</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>46176</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>45370</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45371</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>45371</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45743</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44767</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>45922</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45950</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>45923</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>45398</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45398</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45436</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>45952</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45099</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>46184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>45242</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>45242</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>46184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>46184</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>46184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45656</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>45743</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45596</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46184</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>46184</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45960</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>45968</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45188</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45208</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>46197</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>46197</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44777</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44925</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45749</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45653</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45653</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45733</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45103</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45617</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45253</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45646</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45323</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>46002</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>45777</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>45777</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45288</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>46232</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45504</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>46027</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>46031</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46031</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45792</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>46031</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>45610</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45638</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>45679</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>46150</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45800</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>46052</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>46054</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>46054</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>46054</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>46066</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45103</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>45776</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45817</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45819</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>46295</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>46077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>46295</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>46078</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>46078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>46078</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>46295</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>46295</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46295</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46300</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46086</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45839</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44942</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45532</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45532</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45532</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45846</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46297</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45846</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45848</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46258</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45849</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44971</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>46258</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45855</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45861</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45761</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>46260</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>46260</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>46260</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45478</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45706</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45847</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45873</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>45478</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45337</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45337</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>46260</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45028</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45524</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45631</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46125</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45686</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45440</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45153</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45365</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45091</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45118</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45062</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45091</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45134</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45537</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45639</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45700</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45062</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45062</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45635</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45561</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>44684</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45576</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44925</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45443</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>46260</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45875</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>46307</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45888</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>44994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45726</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45726</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>46309</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44925</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45699</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45510</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45801</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45744</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45810</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>46269</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>46001</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45728</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45504</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45820</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44873</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45205</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45922</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45560</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>44600</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>46000</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44693</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45691</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45246</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>44986</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46149</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44967</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45008</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45706</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45461</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45596</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45096</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45359</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45359</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45204</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45698</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45743</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45743</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45729</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45078</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45719</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45719</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45728</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45071</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45749</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45461</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44851</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44994</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45656</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>45656</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45329</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45756</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45755</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45653</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>44831</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>44997</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>44539</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45014</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45596</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45400</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45275</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>44999</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45587</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45639</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45742</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45659</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45656</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45366</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>45371</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44601</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>44789</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44613</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>44773</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45096</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45632</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45632</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>44726</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45719</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45719</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45749</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45743</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44925</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45743</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45160</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45701</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45729</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45525</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45525</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44593</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45335</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44775</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44895</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45667</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
